--- a/functions and methods.xlsx
+++ b/functions and methods.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dimitar\Documents\Unit 12 - Software Development\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dimitar\Downloads\Dimitar-Unit-12-Task-2-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{608EE8F8-88E6-4E02-A8CE-901C16330063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685718E1-A74E-448E-ABD4-BE691905EAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BB9A533E-49C6-4BFF-804B-BE8AB4108334}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>loadmenu</t>
   </si>
   <si>
-    <t>spawnlocation</t>
-  </si>
-  <si>
     <t>loadsprites</t>
   </si>
   <si>
@@ -111,6 +108,9 @@
   </si>
   <si>
     <t>trainbrake</t>
+  </si>
+  <si>
+    <t>spawnlocation, paramiters</t>
   </si>
 </sst>
 </file>
@@ -533,118 +533,119 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38D63A1-71DD-46E4-BAB6-781B97A8FE67}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.21875" customWidth="1"/>
     <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="C13" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
